--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123721741</v>
+        <v>123719536</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Moberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496602</v>
+        <v>496946</v>
       </c>
       <c r="R2" t="n">
-        <v>6954145</v>
+        <v>6954083</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +790,7 @@
         <v>123721745</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123719536</v>
+        <v>123721741</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +920,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Moberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496946</v>
+        <v>496602</v>
       </c>
       <c r="R4" t="n">
-        <v>6954083</v>
+        <v>6954145</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123719536</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123719536</v>
+        <v>123721741</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Moberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496946</v>
+        <v>496602</v>
       </c>
       <c r="R2" t="n">
-        <v>6954083</v>
+        <v>6954145</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123721745</v>
+        <v>123719536</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Moberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496602</v>
+        <v>496946</v>
       </c>
       <c r="R3" t="n">
-        <v>6954145</v>
+        <v>6954083</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123721741</v>
+        <v>123721745</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,30 +920,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123721741</v>
+        <v>123719536</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Moberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496602</v>
+        <v>496946</v>
       </c>
       <c r="R2" t="n">
-        <v>6954145</v>
+        <v>6954083</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123719536</v>
+        <v>123721741</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Moberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496946</v>
+        <v>496602</v>
       </c>
       <c r="R3" t="n">
-        <v>6954083</v>
+        <v>6954145</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123721741</v>
+        <v>123721745</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,30 +799,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123721745</v>
+        <v>123721741</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,30 +920,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123721741</v>
+        <v>123721745</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -796,42 +791,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123721745</v>
+        <v>123721741</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -920,12 +910,7 @@
         <v>123719536</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16959-2025 artfynd.xlsx
+++ b/artfynd/A 16959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123721745</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123721741</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,8 +1026,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123719536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>